--- a/projects/材料与采购规划.xlsx
+++ b/projects/材料与采购规划.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rd9b8e88a3f6541ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材料总表" sheetId="2" r:id="Rfc5442e1c0ac4cf5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分项预算" sheetId="3" r:id="R9c17a1a3f4264802"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工具与设备" sheetId="4" r:id="R889fe47215374716"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="线上线下同步" sheetId="5" r:id="Rcd4e2af8b1d44c6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="6" r:id="R85adc550462c427a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R7423693ad6374ebb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材料总表" sheetId="2" r:id="R1227d88fbc374fa3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分项预算" sheetId="3" r:id="Rd450ed84555f470e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工具与设备" sheetId="4" r:id="R8ec7531f2875429e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="线上线下同步" sheetId="5" r:id="Rd32c9f6197f14030"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="6" r:id="R6055940e4bba444e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/projects/材料与采购规划.xlsx
+++ b/projects/材料与采购规划.xlsx
@@ -2,12 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R7423693ad6374ebb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材料总表" sheetId="2" r:id="R1227d88fbc374fa3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分项预算" sheetId="3" r:id="Rd450ed84555f470e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工具与设备" sheetId="4" r:id="R8ec7531f2875429e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="线上线下同步" sheetId="5" r:id="Rd32c9f6197f14030"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="6" r:id="R6055940e4bba444e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Ra99ac5711fad499e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材料总表" sheetId="2" r:id="Re207bb8313bc4d60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分项预算" sheetId="3" r:id="R6f259d3706ae40c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="选型评审" sheetId="4" r:id="R47b46b8b289e4134"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工具与设备" sheetId="5" r:id="Rb0feb17813d64bef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="线上线下同步" sheetId="6" r:id="R60dde0911d474ef7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="7" r:id="Rfcd5ae423b45414d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -283,26 +284,26 @@
     <x:xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="200" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="200" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -384,7 +385,7 @@
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="4">
+  <x:dxfs count="8">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -393,6 +394,50 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF375623"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2EFDA"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF1F4E79"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFDEEBF7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7F6000"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF2CC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF375623"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE2EFDA"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -651,7 +696,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="2" t="str">
-        <x:v>更新日期 2026-10-12。材料、存放位置、线上状态一律以本工作簿为准，线下实物改动后回填这里。</x:v>
+        <x:v>更新日期 2026-10-16。材料、存放位置、线上状态一律以本工作簿为准，线下实物改动后回填这里。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="20" customHeight="1">
@@ -675,7 +720,7 @@
         <x:v>材料条目数</x:v>
       </x:c>
       <x:c r="B7" s="60" t="e">
-        <x:f>COUNTA(材料总表!$B$5:$B$101)</x:f>
+        <x:f>COUNTA(材料总表!$B$5:$B$103)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
     </x:row>
@@ -684,7 +729,7 @@
         <x:v>待购条目数</x:v>
       </x:c>
       <x:c r="B8" s="60" t="e">
-        <x:f>COUNTIF(材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>COUNTIF(材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
     </x:row>
@@ -693,7 +738,7 @@
         <x:v>待购预算合计（元）</x:v>
       </x:c>
       <x:c r="B9" s="61" t="e">
-        <x:f>SUMIF(材料总表!$I$5:$I$101,"待购",材料总表!$H$5:$H$101)</x:f>
+        <x:f>SUMIF(材料总表!$I$5:$I$103,"待购",材料总表!$H$5:$H$103)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
     </x:row>
@@ -702,7 +747,7 @@
         <x:v>P0 立即采购（元）</x:v>
       </x:c>
       <x:c r="B10" s="61" t="e">
-        <x:f>SUMIF(材料总表!$J$5:$J$101,"P0 立即采购",材料总表!$H$5:$H$101)</x:f>
+        <x:f>SUMIF(材料总表!$J$5:$J$103,"P0 立即采购",材料总表!$H$5:$H$103)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
     </x:row>
@@ -711,7 +756,7 @@
         <x:v>已有物资参考值（元）</x:v>
       </x:c>
       <x:c r="B11" s="61" t="e">
-        <x:f>SUMIF(材料总表!$I$5:$I$101,"已有",材料总表!$H$5:$H$101)</x:f>
+        <x:f>SUMIF(材料总表!$I$5:$I$103,"已有",材料总表!$H$5:$H$103)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
     </x:row>
@@ -725,7 +770,7 @@
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="37" t="str">
+      <x:c r="A13" s="35" t="str">
         <x:v>已完成项目数</x:v>
       </x:c>
       <x:c r="B13" s="63" t="n">
@@ -774,15 +819,15 @@
         <x:v>成品智能台历（自动翻页 + 温湿度 + 灯带）</x:v>
       </x:c>
       <x:c r="D17" s="28" t="e">
-        <x:f>SUMIFS(材料总表!$H$5:$H$101,材料总表!$B$5:$B$101,$A17,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>SUMIFS(材料总表!$H$5:$H$103,材料总表!$B$5:$B$103,$A17,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="E17" s="28" t="e">
-        <x:f>COUNTIFS(材料总表!$B$5:$B$101,$A17,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>COUNTIFS(材料总表!$B$5:$B$103,$A17,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="F17" s="64" t="e">
-        <x:f>COUNTIF(材料总表!$B$5:$B$101,$A17)</x:f>
+        <x:f>COUNTIF(材料总表!$B$5:$B$103,$A17)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
     </x:row>
@@ -797,15 +842,15 @@
         <x:v>ESP32 折叠键盘中文通信器（B 站投稿）</x:v>
       </x:c>
       <x:c r="D18" s="28" t="e">
-        <x:f>SUMIFS(材料总表!$H$5:$H$101,材料总表!$B$5:$B$101,$A18,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>SUMIFS(材料总表!$H$5:$H$103,材料总表!$B$5:$B$103,$A18,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="E18" s="28" t="e">
-        <x:f>COUNTIFS(材料总表!$B$5:$B$101,$A18,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>COUNTIFS(材料总表!$B$5:$B$103,$A18,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="F18" s="64" t="e">
-        <x:f>COUNTIF(材料总表!$B$5:$B$101,$A18)</x:f>
+        <x:f>COUNTIF(材料总表!$B$5:$B$103,$A18)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
     </x:row>
@@ -820,15 +865,15 @@
         <x:v>1:1000 LZ127 复刻模型 + 开源图纸</x:v>
       </x:c>
       <x:c r="D19" s="28" t="e">
-        <x:f>SUMIFS(材料总表!$H$5:$H$101,材料总表!$B$5:$B$101,$A19,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>SUMIFS(材料总表!$H$5:$H$103,材料总表!$B$5:$B$103,$A19,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="E19" s="28" t="e">
-        <x:f>COUNTIFS(材料总表!$B$5:$B$101,$A19,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>COUNTIFS(材料总表!$B$5:$B$103,$A19,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="F19" s="64" t="e">
-        <x:f>COUNTIF(材料总表!$B$5:$B$101,$A19)</x:f>
+        <x:f>COUNTIF(材料总表!$B$5:$B$103,$A19)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
     </x:row>
@@ -843,15 +888,15 @@
         <x:v>新月形飞翼概念机 3D 打印模型</x:v>
       </x:c>
       <x:c r="D20" s="28" t="e">
-        <x:f>SUMIFS(材料总表!$H$5:$H$101,材料总表!$B$5:$B$101,$A20,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>SUMIFS(材料总表!$H$5:$H$103,材料总表!$B$5:$B$103,$A20,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="E20" s="28" t="e">
-        <x:f>COUNTIFS(材料总表!$B$5:$B$101,$A20,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>COUNTIFS(材料总表!$B$5:$B$103,$A20,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="F20" s="64" t="e">
-        <x:f>COUNTIF(材料总表!$B$5:$B$101,$A20)</x:f>
+        <x:f>COUNTIF(材料总表!$B$5:$B$103,$A20)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
     </x:row>
@@ -866,15 +911,15 @@
         <x:v>24 路电磁铁阵列自动演奏装置</x:v>
       </x:c>
       <x:c r="D21" s="28" t="e">
-        <x:f>SUMIFS(材料总表!$H$5:$H$101,材料总表!$B$5:$B$101,$A21,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>SUMIFS(材料总表!$H$5:$H$103,材料总表!$B$5:$B$103,$A21,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="E21" s="28" t="e">
-        <x:f>COUNTIFS(材料总表!$B$5:$B$101,$A21,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>COUNTIFS(材料总表!$B$5:$B$103,$A21,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="F21" s="64" t="e">
-        <x:f>COUNTIF(材料总表!$B$5:$B$101,$A21)</x:f>
+        <x:f>COUNTIF(材料总表!$B$5:$B$103,$A21)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
     </x:row>
@@ -889,15 +934,15 @@
         <x:v>助力外骨骼原型（先做单腿/单臂）</x:v>
       </x:c>
       <x:c r="D22" s="28" t="e">
-        <x:f>SUMIFS(材料总表!$H$5:$H$101,材料总表!$B$5:$B$101,$A22,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>SUMIFS(材料总表!$H$5:$H$103,材料总表!$B$5:$B$103,$A22,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="E22" s="28" t="e">
-        <x:f>COUNTIFS(材料总表!$B$5:$B$101,$A22,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>COUNTIFS(材料总表!$B$5:$B$103,$A22,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="F22" s="64" t="e">
-        <x:f>COUNTIF(材料总表!$B$5:$B$101,$A22)</x:f>
+        <x:f>COUNTIF(材料总表!$B$5:$B$103,$A22)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
     </x:row>
@@ -912,15 +957,15 @@
         <x:v>喷笔 + 气泵涂装工位</x:v>
       </x:c>
       <x:c r="D23" s="28" t="e">
-        <x:f>SUMIFS(材料总表!$H$5:$H$101,材料总表!$B$5:$B$101,$A23,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>SUMIFS(材料总表!$H$5:$H$103,材料总表!$B$5:$B$103,$A23,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="E23" s="28" t="e">
-        <x:f>COUNTIFS(材料总表!$B$5:$B$101,$A23,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>COUNTIFS(材料总表!$B$5:$B$103,$A23,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="F23" s="64" t="e">
-        <x:f>COUNTIF(材料总表!$B$5:$B$101,$A23)</x:f>
+        <x:f>COUNTIF(材料总表!$B$5:$B$103,$A23)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
     </x:row>
@@ -935,15 +980,15 @@
         <x:v>2-3 分钟自我介绍故事短片</x:v>
       </x:c>
       <x:c r="D24" s="28" t="e">
-        <x:f>SUMIFS(材料总表!$H$5:$H$101,材料总表!$B$5:$B$101,$A24,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>SUMIFS(材料总表!$H$5:$H$103,材料总表!$B$5:$B$103,$A24,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="E24" s="28" t="e">
-        <x:f>COUNTIFS(材料总表!$B$5:$B$101,$A24,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>COUNTIFS(材料总表!$B$5:$B$103,$A24,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="F24" s="64" t="e">
-        <x:f>COUNTIF(材料总表!$B$5:$B$101,$A24)</x:f>
+        <x:f>COUNTIF(材料总表!$B$5:$B$103,$A24)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
     </x:row>
@@ -958,15 +1003,15 @@
         <x:v>现实主义生存机制 Minecraft Forge 模组</x:v>
       </x:c>
       <x:c r="D25" s="28" t="e">
-        <x:f>SUMIFS(材料总表!$H$5:$H$101,材料总表!$B$5:$B$101,$A25,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>SUMIFS(材料总表!$H$5:$H$103,材料总表!$B$5:$B$103,$A25,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="E25" s="28" t="e">
-        <x:f>COUNTIFS(材料总表!$B$5:$B$101,$A25,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>COUNTIFS(材料总表!$B$5:$B$103,$A25,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="F25" s="64" t="e">
-        <x:f>COUNTIF(材料总表!$B$5:$B$101,$A25)</x:f>
+        <x:f>COUNTIF(材料总表!$B$5:$B$103,$A25)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
     </x:row>
@@ -1074,13 +1119,24 @@
       </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="37" t="str">
+      <x:c r="A36" s="24" t="str">
+        <x:v>下单前再比一次价</x:v>
+      </x:c>
+      <x:c r="B36" s="25" t="str">
+        <x:v>全部待购项</x:v>
+      </x:c>
+      <x:c r="C36" s="29" t="str">
+        <x:v>本表的单价是讨论里的参考价，实际以淘宝/拼多多到手价为准，差价回填到材料总表</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="35" t="str">
         <x:v>本表已入库并推送</x:v>
       </x:c>
-      <x:c r="B36" s="38" t="str">
+      <x:c r="B37" s="36" t="str">
         <x:v>全部项目</x:v>
       </x:c>
-      <x:c r="C36" s="41" t="str">
+      <x:c r="C37" s="37" t="str">
         <x:v>以后改材料先改本表，再改线上文案；桌面副本会随仓库一起更新</x:v>
       </x:c>
     </x:row>
@@ -1112,7 +1168,7 @@
   <x:sheetData>
     <x:row r="2">
       <x:c r="A2" s="1" t="str">
-        <x:v>材料总表（全部 9 个 DIY 项目，共 97 条）</x:v>
+        <x:v>材料总表（全部 9 个 DIY 项目，共 99 条）</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3942,7 +3998,7 @@
         <x:v>驱动舵机</x:v>
       </x:c>
       <x:c r="D75" s="25" t="str">
-        <x:v>大扭矩串行舵机 70kg·cm 以上</x:v>
+        <x:v>国产 70kg·cm 级串行舵机（LX-224 同级）</x:v>
       </x:c>
       <x:c r="E75" s="26" t="n">
         <x:v>2</x:v>
@@ -3951,11 +4007,11 @@
         <x:v>个</x:v>
       </x:c>
       <x:c r="G75" s="28" t="n">
-        <x:v>650</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H75" s="28" t="n">
         <x:f>IF(OR(G75="",G75=0),"",E75*G75)</x:f>
-        <x:v>1300</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="I75" s="27" t="str">
         <x:v>待购</x:v>
@@ -3967,7 +4023,7 @@
         <x:v>待定</x:v>
       </x:c>
       <x:c r="L75" s="29" t="str">
-        <x:v>原「高速空心杯」方案已否，改用串行舵机</x:v>
+        <x:v>原估 650/个；讨论原文价位是 200-400/个</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -3982,7 +4038,7 @@
         <x:v>主控</x:v>
       </x:c>
       <x:c r="D76" s="25" t="str">
-        <x:v>Arduino Mega 2560</x:v>
+        <x:v>Arduino Mega 2560（国产兼容板）</x:v>
       </x:c>
       <x:c r="E76" s="26" t="n">
         <x:v>1</x:v>
@@ -3991,11 +4047,11 @@
         <x:v>块</x:v>
       </x:c>
       <x:c r="G76" s="28" t="n">
-        <x:v>120</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H76" s="28" t="n">
         <x:f>IF(OR(G76="",G76=0),"",E76*G76)</x:f>
-        <x:v>120</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I76" s="27" t="str">
         <x:v>待购</x:v>
@@ -4007,7 +4063,7 @@
         <x:v>电子元件盒 D</x:v>
       </x:c>
       <x:c r="L76" s="29" t="str">
-        <x:v>接口丰富，需配舵机通信转换板</x:v>
+        <x:v>原估 120；原文「国产板 50 元」，引脚完全一致</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -4188,11 +4244,11 @@
         <x:v>根</x:v>
       </x:c>
       <x:c r="G81" s="28" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H81" s="28" t="n">
         <x:f>IF(OR(G81="",G81=0),"",E81*G81)</x:f>
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I81" s="27" t="str">
         <x:v>待购</x:v>
@@ -4204,7 +4260,7 @@
         <x:v>材料箱（管材）</x:v>
       </x:c>
       <x:c r="L81" s="29" t="str">
-        <x:v>关键应力处夹内芯</x:v>
+        <x:v>原估 10/根，原文「5 元一根」；关键应力处夹内芯</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -4227,9 +4283,12 @@
       <x:c r="F82" s="27" t="str">
         <x:v>个</x:v>
       </x:c>
-      <x:c r="G82" s="28" t="str"/>
-      <x:c r="H82" s="28" t="str">
+      <x:c r="G82" s="28" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H82" s="28" t="n">
         <x:f>IF(OR(G82="",G82=0),"",E82*G82)</x:f>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I82" s="27" t="str">
         <x:v>待购</x:v>
@@ -4241,7 +4300,7 @@
         <x:v>材料箱（五金）</x:v>
       </x:c>
       <x:c r="L82" s="29" t="str">
-        <x:v>降低关节摩擦</x:v>
+        <x:v>原先未标价；防打印件被压裂的关键件</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -4253,23 +4312,23 @@
         <x:v>助力外骨骼</x:v>
       </x:c>
       <x:c r="C83" s="25" t="str">
-        <x:v>固定绑带</x:v>
+        <x:v>脚底压力开关</x:v>
       </x:c>
       <x:c r="D83" s="25" t="str">
-        <x:v>宽腰带 / 大腿绑带</x:v>
+        <x:v>薄膜压力开关</x:v>
       </x:c>
       <x:c r="E83" s="26" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F83" s="27" t="str">
-        <x:v>套</x:v>
+        <x:v>个</x:v>
       </x:c>
       <x:c r="G83" s="28" t="n">
-        <x:v>50</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H83" s="28" t="n">
         <x:f>IF(OR(G83="",G83=0),"",E83*G83)</x:f>
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I83" s="27" t="str">
         <x:v>待购</x:v>
@@ -4278,9 +4337,11 @@
         <x:v>P1 确认后</x:v>
       </x:c>
       <x:c r="K83" s="25" t="str">
-        <x:v>待定</x:v>
-      </x:c>
-      <x:c r="L83" s="29" t="str"/>
+        <x:v>电子元件盒 D</x:v>
+      </x:c>
+      <x:c r="L83" s="29" t="str">
+        <x:v>姿态跟随触发用，比力传感器便宜两个数量级</x:v>
+      </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="24" t="n">
@@ -4291,36 +4352,34 @@
         <x:v>助力外骨骼</x:v>
       </x:c>
       <x:c r="C84" s="25" t="str">
-        <x:v>电池组</x:v>
+        <x:v>固定绑带</x:v>
       </x:c>
       <x:c r="D84" s="25" t="str">
-        <x:v>12V 锂电池组</x:v>
+        <x:v>宽腰带 / 大腿绑带</x:v>
       </x:c>
       <x:c r="E84" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F84" s="27" t="str">
-        <x:v>组</x:v>
+        <x:v>套</x:v>
       </x:c>
       <x:c r="G84" s="28" t="n">
-        <x:v>200</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H84" s="28" t="n">
         <x:f>IF(OR(G84="",G84=0),"",E84*G84)</x:f>
-        <x:v>200</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I84" s="27" t="str">
         <x:v>待购</x:v>
       </x:c>
       <x:c r="J84" s="27" t="str">
-        <x:v>P2 后期/可选</x:v>
+        <x:v>P1 确认后</x:v>
       </x:c>
       <x:c r="K84" s="25" t="str">
         <x:v>待定</x:v>
       </x:c>
-      <x:c r="L84" s="29" t="str">
-        <x:v>给舵机供电</x:v>
-      </x:c>
+      <x:c r="L84" s="29" t="str"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="24" t="n">
@@ -4331,34 +4390,36 @@
         <x:v>助力外骨骼</x:v>
       </x:c>
       <x:c r="C85" s="25" t="str">
-        <x:v>紧固件</x:v>
+        <x:v>电池组</x:v>
       </x:c>
       <x:c r="D85" s="25" t="str">
-        <x:v>螺丝 / 螺母 / 鱼眼轴承</x:v>
+        <x:v>12V 锂电池组</x:v>
       </x:c>
       <x:c r="E85" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F85" s="27" t="str">
-        <x:v>批</x:v>
+        <x:v>组</x:v>
       </x:c>
       <x:c r="G85" s="28" t="n">
-        <x:v>100</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="H85" s="28" t="n">
         <x:f>IF(OR(G85="",G85=0),"",E85*G85)</x:f>
-        <x:v>100</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="I85" s="27" t="str">
         <x:v>待购</x:v>
       </x:c>
       <x:c r="J85" s="27" t="str">
-        <x:v>P1 确认后</x:v>
+        <x:v>P2 后期/可选</x:v>
       </x:c>
       <x:c r="K85" s="25" t="str">
-        <x:v>材料箱（五金）</x:v>
-      </x:c>
-      <x:c r="L85" s="29" t="str"/>
+        <x:v>待定</x:v>
+      </x:c>
+      <x:c r="L85" s="29" t="str">
+        <x:v>给舵机供电</x:v>
+      </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="24" t="n">
@@ -4366,39 +4427,37 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B86" s="25" t="str">
-        <x:v>模型涂装</x:v>
+        <x:v>助力外骨骼</x:v>
       </x:c>
       <x:c r="C86" s="25" t="str">
-        <x:v>喷笔</x:v>
+        <x:v>紧固件</x:v>
       </x:c>
       <x:c r="D86" s="25" t="str">
-        <x:v>0.3mm 双动式</x:v>
+        <x:v>螺丝 / 螺母 / 鱼眼轴承</x:v>
       </x:c>
       <x:c r="E86" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F86" s="27" t="str">
-        <x:v>支</x:v>
+        <x:v>批</x:v>
       </x:c>
       <x:c r="G86" s="28" t="n">
-        <x:v>200</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H86" s="28" t="n">
         <x:f>IF(OR(G86="",G86=0),"",E86*G86)</x:f>
-        <x:v>200</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I86" s="27" t="str">
         <x:v>待购</x:v>
       </x:c>
       <x:c r="J86" s="27" t="str">
-        <x:v>P2 后期/可选</x:v>
+        <x:v>P1 确认后</x:v>
       </x:c>
       <x:c r="K86" s="25" t="str">
-        <x:v>待定</x:v>
-      </x:c>
-      <x:c r="L86" s="29" t="str">
-        <x:v>精细涂装核心装备</x:v>
-      </x:c>
+        <x:v>材料箱（五金）</x:v>
+      </x:c>
+      <x:c r="L86" s="29" t="str"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="24" t="n">
@@ -4409,23 +4468,23 @@
         <x:v>模型涂装</x:v>
       </x:c>
       <x:c r="C87" s="25" t="str">
-        <x:v>气泵</x:v>
+        <x:v>喷笔</x:v>
       </x:c>
       <x:c r="D87" s="25" t="str">
-        <x:v>带储气罐（如浩盛 AF186）</x:v>
+        <x:v>优速达 S-130 0.3mm 双动（可加 HD-130 0.5mm，约 80 元）</x:v>
       </x:c>
       <x:c r="E87" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F87" s="27" t="str">
-        <x:v>台</x:v>
+        <x:v>支</x:v>
       </x:c>
       <x:c r="G87" s="28" t="n">
-        <x:v>400</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H87" s="28" t="n">
         <x:f>IF(OR(G87="",G87=0),"",E87*G87)</x:f>
-        <x:v>400</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="I87" s="27" t="str">
         <x:v>待购</x:v>
@@ -4437,7 +4496,7 @@
         <x:v>待定</x:v>
       </x:c>
       <x:c r="L87" s="29" t="str">
-        <x:v>带罐才能消除喷涂脉冲</x:v>
+        <x:v>原估 200；优速达是原文列出的国产高性价比型号</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -4449,23 +4508,23 @@
         <x:v>模型涂装</x:v>
       </x:c>
       <x:c r="C88" s="25" t="str">
-        <x:v>油水分离器</x:v>
+        <x:v>气泵</x:v>
       </x:c>
       <x:c r="D88" s="25" t="str">
-        <x:v>1 个</x:v>
+        <x:v>浩盛 AF186 mini 带储气罐</x:v>
       </x:c>
       <x:c r="E88" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F88" s="27" t="str">
-        <x:v>个</x:v>
+        <x:v>台</x:v>
       </x:c>
       <x:c r="G88" s="28" t="n">
-        <x:v>40</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="H88" s="28" t="n">
         <x:f>IF(OR(G88="",G88=0),"",E88*G88)</x:f>
-        <x:v>40</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="I88" s="27" t="str">
         <x:v>待购</x:v>
@@ -4477,7 +4536,7 @@
         <x:v>待定</x:v>
       </x:c>
       <x:c r="L88" s="29" t="str">
-        <x:v>防喷水</x:v>
+        <x:v>原估 400；原文给的价格区间是 180-600 元，不必顶到上限</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -4489,23 +4548,23 @@
         <x:v>模型涂装</x:v>
       </x:c>
       <x:c r="C89" s="25" t="str">
-        <x:v>模型漆</x:v>
+        <x:v>油水分离器</x:v>
       </x:c>
       <x:c r="D89" s="25" t="str">
-        <x:v>水性 / 硝基漆</x:v>
+        <x:v>1 个</x:v>
       </x:c>
       <x:c r="E89" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F89" s="27" t="str">
-        <x:v>套</x:v>
+        <x:v>个</x:v>
       </x:c>
       <x:c r="G89" s="28" t="n">
-        <x:v>150</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H89" s="28" t="n">
         <x:f>IF(OR(G89="",G89=0),"",E89*G89)</x:f>
-        <x:v>150</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I89" s="27" t="str">
         <x:v>待购</x:v>
@@ -4514,10 +4573,10 @@
         <x:v>P2 后期/可选</x:v>
       </x:c>
       <x:c r="K89" s="25" t="str">
-        <x:v>耗材盒</x:v>
+        <x:v>待定</x:v>
       </x:c>
       <x:c r="L89" s="29" t="str">
-        <x:v>与飞艇涂装共用</x:v>
+        <x:v>防喷水</x:v>
       </x:c>
     </x:row>
     <x:row r="90">
@@ -4529,10 +4588,10 @@
         <x:v>模型涂装</x:v>
       </x:c>
       <x:c r="C90" s="25" t="str">
-        <x:v>稀释剂与洗笔液</x:v>
+        <x:v>模型漆</x:v>
       </x:c>
       <x:c r="D90" s="25" t="str">
-        <x:v>1 套</x:v>
+        <x:v>郡士 H 系 / Vallejo 水性漆，约 12 元/瓶 × 8 瓶</x:v>
       </x:c>
       <x:c r="E90" s="26" t="n">
         <x:v>1</x:v>
@@ -4541,11 +4600,11 @@
         <x:v>套</x:v>
       </x:c>
       <x:c r="G90" s="28" t="n">
-        <x:v>40</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="H90" s="28" t="n">
         <x:f>IF(OR(G90="",G90=0),"",E90*G90)</x:f>
-        <x:v>40</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="I90" s="27" t="str">
         <x:v>待购</x:v>
@@ -4556,7 +4615,9 @@
       <x:c r="K90" s="25" t="str">
         <x:v>耗材盒</x:v>
       </x:c>
-      <x:c r="L90" s="29" t="str"/>
+      <x:c r="L90" s="29" t="str">
+        <x:v>原估整套 150；按需买色号更省，与飞艇涂装共用</x:v>
+      </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="24" t="n">
@@ -4567,10 +4628,10 @@
         <x:v>模型涂装</x:v>
       </x:c>
       <x:c r="C91" s="25" t="str">
-        <x:v>防护装备</x:v>
+        <x:v>稀释剂与洗笔液</x:v>
       </x:c>
       <x:c r="D91" s="25" t="str">
-        <x:v>防毒面具 + 手套</x:v>
+        <x:v>1 套</x:v>
       </x:c>
       <x:c r="E91" s="26" t="n">
         <x:v>1</x:v>
@@ -4579,24 +4640,22 @@
         <x:v>套</x:v>
       </x:c>
       <x:c r="G91" s="28" t="n">
-        <x:v>60</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H91" s="28" t="n">
         <x:f>IF(OR(G91="",G91=0),"",E91*G91)</x:f>
-        <x:v>60</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I91" s="27" t="str">
         <x:v>待购</x:v>
       </x:c>
       <x:c r="J91" s="27" t="str">
-        <x:v>P1 确认后</x:v>
+        <x:v>P2 后期/可选</x:v>
       </x:c>
       <x:c r="K91" s="25" t="str">
-        <x:v>待定</x:v>
-      </x:c>
-      <x:c r="L91" s="29" t="str">
-        <x:v>必须佩戴，不可省</x:v>
-      </x:c>
+        <x:v>耗材盒</x:v>
+      </x:c>
+      <x:c r="L91" s="29" t="str"/>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="24" t="n">
@@ -4607,34 +4666,36 @@
         <x:v>模型涂装</x:v>
       </x:c>
       <x:c r="C92" s="25" t="str">
-        <x:v>喷涂转台</x:v>
+        <x:v>防护装备</x:v>
       </x:c>
       <x:c r="D92" s="25" t="str">
-        <x:v>1 个</x:v>
+        <x:v>防毒面具 + 手套</x:v>
       </x:c>
       <x:c r="E92" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F92" s="27" t="str">
-        <x:v>个</x:v>
+        <x:v>套</x:v>
       </x:c>
       <x:c r="G92" s="28" t="n">
-        <x:v>40</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H92" s="28" t="n">
         <x:f>IF(OR(G92="",G92=0),"",E92*G92)</x:f>
-        <x:v>40</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I92" s="27" t="str">
         <x:v>待购</x:v>
       </x:c>
       <x:c r="J92" s="27" t="str">
-        <x:v>P2 后期/可选</x:v>
+        <x:v>P1 确认后</x:v>
       </x:c>
       <x:c r="K92" s="25" t="str">
         <x:v>待定</x:v>
       </x:c>
-      <x:c r="L92" s="29" t="str"/>
+      <x:c r="L92" s="29" t="str">
+        <x:v>必须佩戴，不可省</x:v>
+      </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="24" t="n">
@@ -4645,23 +4706,23 @@
         <x:v>模型涂装</x:v>
       </x:c>
       <x:c r="C93" s="25" t="str">
-        <x:v>排风抽风机</x:v>
+        <x:v>喷涂转台</x:v>
       </x:c>
       <x:c r="D93" s="25" t="str">
-        <x:v>1 台</x:v>
+        <x:v>1 个</x:v>
       </x:c>
       <x:c r="E93" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F93" s="27" t="str">
-        <x:v>台</x:v>
+        <x:v>个</x:v>
       </x:c>
       <x:c r="G93" s="28" t="n">
-        <x:v>100</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H93" s="28" t="n">
         <x:f>IF(OR(G93="",G93=0),"",E93*G93)</x:f>
-        <x:v>100</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I93" s="27" t="str">
         <x:v>待购</x:v>
@@ -4670,11 +4731,9 @@
         <x:v>P2 后期/可选</x:v>
       </x:c>
       <x:c r="K93" s="25" t="str">
-        <x:v>阳台工作台</x:v>
-      </x:c>
-      <x:c r="L93" s="29" t="str">
-        <x:v>阳台作业更安全</x:v>
-      </x:c>
+        <x:v>待定</x:v>
+      </x:c>
+      <x:c r="L93" s="29" t="str"/>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="24" t="n">
@@ -4685,35 +4744,35 @@
         <x:v>模型涂装</x:v>
       </x:c>
       <x:c r="C94" s="25" t="str">
-        <x:v>喷罐（入门替代）</x:v>
+        <x:v>负压喷漆箱（自制）</x:v>
       </x:c>
       <x:c r="D94" s="25" t="str">
-        <x:v>补土用喷罐</x:v>
+        <x:v>含风机、LED 灯条、过滤棉</x:v>
       </x:c>
       <x:c r="E94" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F94" s="27" t="str">
-        <x:v>罐</x:v>
+        <x:v>套</x:v>
       </x:c>
       <x:c r="G94" s="28" t="n">
-        <x:v>30</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="H94" s="28" t="n">
         <x:f>IF(OR(G94="",G94=0),"",E94*G94)</x:f>
-        <x:v>30</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="I94" s="27" t="str">
         <x:v>待购</x:v>
       </x:c>
       <x:c r="J94" s="27" t="str">
-        <x:v>P0 立即采购</x:v>
+        <x:v>P2 后期/可选</x:v>
       </x:c>
       <x:c r="K94" s="25" t="str">
-        <x:v>待定</x:v>
+        <x:v>阳台工作台</x:v>
       </x:c>
       <x:c r="L94" s="29" t="str">
-        <x:v>先试水可只买这一项</x:v>
+        <x:v>原写「排风抽风机 100」；负压箱挡漆雾效果好得多（原文有 100 元自制方案）</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
@@ -4722,37 +4781,38 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="B95" s="25" t="str">
-        <x:v>自我介绍视频</x:v>
+        <x:v>模型涂装</x:v>
       </x:c>
       <x:c r="C95" s="25" t="str">
-        <x:v>拍摄设备</x:v>
+        <x:v>（可选）手持充电喷笔套装</x:v>
       </x:c>
       <x:c r="D95" s="25" t="str">
-        <x:v>手机 / 相机</x:v>
+        <x:v>无需气泵，约 74-200 元</x:v>
       </x:c>
       <x:c r="E95" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F95" s="27" t="str">
-        <x:v>台</x:v>
+        <x:v>套</x:v>
       </x:c>
       <x:c r="G95" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H95" s="28" t="str">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H95" s="28" t="n">
         <x:f>IF(OR(G95="",G95=0),"",E95*G95)</x:f>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="I95" s="27" t="str">
-        <x:v>已有</x:v>
+        <x:v>可选</x:v>
       </x:c>
       <x:c r="J95" s="27" t="str">
-        <x:v>—</x:v>
+        <x:v>P2 后期/可选</x:v>
       </x:c>
       <x:c r="K95" s="25" t="str">
-        <x:v>—</x:v>
+        <x:v>待定</x:v>
       </x:c>
       <x:c r="L95" s="29" t="str">
-        <x:v>用现有设备即可</x:v>
+        <x:v>与喷笔 + 气泵二选一，先试水用</x:v>
       </x:c>
     </x:row>
     <x:row r="96">
@@ -4761,38 +4821,38 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B96" s="25" t="str">
-        <x:v>自我介绍视频</x:v>
+        <x:v>模型涂装</x:v>
       </x:c>
       <x:c r="C96" s="25" t="str">
-        <x:v>领夹麦克风</x:v>
+        <x:v>喷罐（入门替代）</x:v>
       </x:c>
       <x:c r="D96" s="25" t="str">
-        <x:v>有线 / 无线</x:v>
+        <x:v>补土用喷罐</x:v>
       </x:c>
       <x:c r="E96" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F96" s="27" t="str">
-        <x:v>个</x:v>
+        <x:v>罐</x:v>
       </x:c>
       <x:c r="G96" s="28" t="n">
-        <x:v>80</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="H96" s="28" t="n">
         <x:f>IF(OR(G96="",G96=0),"",E96*G96)</x:f>
-        <x:v>80</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I96" s="27" t="str">
         <x:v>待购</x:v>
       </x:c>
       <x:c r="J96" s="27" t="str">
-        <x:v>P1 确认后</x:v>
+        <x:v>P0 立即采购</x:v>
       </x:c>
       <x:c r="K96" s="25" t="str">
         <x:v>待定</x:v>
       </x:c>
       <x:c r="L96" s="29" t="str">
-        <x:v>旁白自己录，收音比画面重要</x:v>
+        <x:v>先试水可只买这一项</x:v>
       </x:c>
     </x:row>
     <x:row r="97">
@@ -4804,35 +4864,34 @@
         <x:v>自我介绍视频</x:v>
       </x:c>
       <x:c r="C97" s="25" t="str">
-        <x:v>补光灯</x:v>
+        <x:v>拍摄设备</x:v>
       </x:c>
       <x:c r="D97" s="25" t="str">
-        <x:v>便携 LED</x:v>
+        <x:v>手机 / 相机</x:v>
       </x:c>
       <x:c r="E97" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F97" s="27" t="str">
-        <x:v>个</x:v>
+        <x:v>台</x:v>
       </x:c>
       <x:c r="G97" s="28" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="H97" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H97" s="28" t="str">
         <x:f>IF(OR(G97="",G97=0),"",E97*G97)</x:f>
-        <x:v>60</x:v>
       </x:c>
       <x:c r="I97" s="27" t="str">
-        <x:v>待购</x:v>
+        <x:v>已有</x:v>
       </x:c>
       <x:c r="J97" s="27" t="str">
-        <x:v>P1 确认后</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="K97" s="25" t="str">
-        <x:v>待定</x:v>
+        <x:v>—</x:v>
       </x:c>
       <x:c r="L97" s="29" t="str">
-        <x:v>室内补光；也可全用自然光</x:v>
+        <x:v>用现有设备即可</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -4844,10 +4903,10 @@
         <x:v>自我介绍视频</x:v>
       </x:c>
       <x:c r="C98" s="25" t="str">
-        <x:v>三脚架 / 手机支架</x:v>
+        <x:v>领夹麦克风</x:v>
       </x:c>
       <x:c r="D98" s="25" t="str">
-        <x:v>1 个</x:v>
+        <x:v>有线 / 无线</x:v>
       </x:c>
       <x:c r="E98" s="26" t="n">
         <x:v>1</x:v>
@@ -4856,11 +4915,11 @@
         <x:v>个</x:v>
       </x:c>
       <x:c r="G98" s="28" t="n">
-        <x:v>40</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H98" s="28" t="n">
         <x:f>IF(OR(G98="",G98=0),"",E98*G98)</x:f>
-        <x:v>40</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="I98" s="27" t="str">
         <x:v>待购</x:v>
@@ -4872,7 +4931,7 @@
         <x:v>待定</x:v>
       </x:c>
       <x:c r="L98" s="29" t="str">
-        <x:v>固定机位，起床镜头要用</x:v>
+        <x:v>旁白自己录，收音比画面重要</x:v>
       </x:c>
     </x:row>
     <x:row r="99">
@@ -4884,34 +4943,35 @@
         <x:v>自我介绍视频</x:v>
       </x:c>
       <x:c r="C99" s="25" t="str">
-        <x:v>剪辑软件</x:v>
+        <x:v>补光灯</x:v>
       </x:c>
       <x:c r="D99" s="25" t="str">
-        <x:v>DaVinci Resolve / 剪映</x:v>
+        <x:v>便携 LED</x:v>
       </x:c>
       <x:c r="E99" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F99" s="27" t="str">
-        <x:v>套</x:v>
+        <x:v>个</x:v>
       </x:c>
       <x:c r="G99" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H99" s="28" t="str">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H99" s="28" t="n">
         <x:f>IF(OR(G99="",G99=0),"",E99*G99)</x:f>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I99" s="27" t="str">
-        <x:v>已有</x:v>
+        <x:v>待购</x:v>
       </x:c>
       <x:c r="J99" s="27" t="str">
-        <x:v>—</x:v>
+        <x:v>P1 确认后</x:v>
       </x:c>
       <x:c r="K99" s="25" t="str">
-        <x:v>电脑</x:v>
+        <x:v>待定</x:v>
       </x:c>
       <x:c r="L99" s="29" t="str">
-        <x:v>免费版即可；达芬奇对显卡有要求</x:v>
+        <x:v>室内补光；也可全用自然光</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -4920,37 +4980,38 @@
         <x:v>96</x:v>
       </x:c>
       <x:c r="B100" s="25" t="str">
-        <x:v>Minecraft模组</x:v>
+        <x:v>自我介绍视频</x:v>
       </x:c>
       <x:c r="C100" s="25" t="str">
-        <x:v>开发环境</x:v>
+        <x:v>三脚架 / 手机支架</x:v>
       </x:c>
       <x:c r="D100" s="25" t="str">
-        <x:v>IDEA + Forge MDK</x:v>
+        <x:v>1 个</x:v>
       </x:c>
       <x:c r="E100" s="26" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F100" s="27" t="str">
-        <x:v>套</x:v>
+        <x:v>个</x:v>
       </x:c>
       <x:c r="G100" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H100" s="28" t="str">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="H100" s="28" t="n">
         <x:f>IF(OR(G100="",G100=0),"",E100*G100)</x:f>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I100" s="27" t="str">
-        <x:v>无需采购</x:v>
+        <x:v>待购</x:v>
       </x:c>
       <x:c r="J100" s="27" t="str">
-        <x:v>—</x:v>
+        <x:v>P1 确认后</x:v>
       </x:c>
       <x:c r="K100" s="25" t="str">
-        <x:v>电脑</x:v>
+        <x:v>待定</x:v>
       </x:c>
       <x:c r="L100" s="29" t="str">
-        <x:v>建议 Forge 1.20.1，生态最全</x:v>
+        <x:v>固定机位，起床镜头要用</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -4959,19 +5020,19 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="B101" s="25" t="str">
-        <x:v>Minecraft模组</x:v>
+        <x:v>自我介绍视频</x:v>
       </x:c>
       <x:c r="C101" s="25" t="str">
-        <x:v>实物材料</x:v>
+        <x:v>剪辑软件</x:v>
       </x:c>
       <x:c r="D101" s="25" t="str">
-        <x:v>纯软件项目</x:v>
+        <x:v>DaVinci Resolve / 剪映</x:v>
       </x:c>
       <x:c r="E101" s="26" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F101" s="27" t="str">
-        <x:v>—</x:v>
+        <x:v>套</x:v>
       </x:c>
       <x:c r="G101" s="28" t="n">
         <x:v>0</x:v>
@@ -4980,54 +5041,132 @@
         <x:f>IF(OR(G101="",G101=0),"",E101*G101)</x:f>
       </x:c>
       <x:c r="I101" s="27" t="str">
-        <x:v>无需采购</x:v>
+        <x:v>已有</x:v>
       </x:c>
       <x:c r="J101" s="27" t="str">
         <x:v>—</x:v>
       </x:c>
       <x:c r="K101" s="25" t="str">
+        <x:v>电脑</x:v>
+      </x:c>
+      <x:c r="L101" s="29" t="str">
+        <x:v>免费版即可；达芬奇对显卡有要求</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="24" t="n">
+        <x:f>ROW()-4</x:f>
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B102" s="25" t="str">
+        <x:v>Minecraft模组</x:v>
+      </x:c>
+      <x:c r="C102" s="25" t="str">
+        <x:v>开发环境</x:v>
+      </x:c>
+      <x:c r="D102" s="25" t="str">
+        <x:v>IDEA + Forge MDK</x:v>
+      </x:c>
+      <x:c r="E102" s="26" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F102" s="27" t="str">
+        <x:v>套</x:v>
+      </x:c>
+      <x:c r="G102" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H102" s="28" t="str">
+        <x:f>IF(OR(G102="",G102=0),"",E102*G102)</x:f>
+      </x:c>
+      <x:c r="I102" s="27" t="str">
+        <x:v>无需采购</x:v>
+      </x:c>
+      <x:c r="J102" s="27" t="str">
         <x:v>—</x:v>
       </x:c>
-      <x:c r="L101" s="29" t="str">
+      <x:c r="K102" s="25" t="str">
+        <x:v>电脑</x:v>
+      </x:c>
+      <x:c r="L102" s="29" t="str">
+        <x:v>建议 Forge 1.20.1，生态最全</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="24" t="n">
+        <x:f>ROW()-4</x:f>
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B103" s="25" t="str">
+        <x:v>Minecraft模组</x:v>
+      </x:c>
+      <x:c r="C103" s="25" t="str">
+        <x:v>实物材料</x:v>
+      </x:c>
+      <x:c r="D103" s="25" t="str">
+        <x:v>纯软件项目</x:v>
+      </x:c>
+      <x:c r="E103" s="26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F103" s="27" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="G103" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H103" s="28" t="str">
+        <x:f>IF(OR(G103="",G103=0),"",E103*G103)</x:f>
+      </x:c>
+      <x:c r="I103" s="27" t="str">
+        <x:v>无需采购</x:v>
+      </x:c>
+      <x:c r="J103" s="27" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="K103" s="25" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L103" s="29" t="str">
         <x:v>不需要实物材料</x:v>
       </x:c>
     </x:row>
-    <x:row r="102">
-      <x:c r="A102" s="30" t="str">
+    <x:row r="104">
+      <x:c r="A104" s="30" t="str">
         <x:v>合计</x:v>
       </x:c>
-      <x:c r="B102" s="31"/>
-      <x:c r="C102" s="31"/>
-      <x:c r="D102" s="31"/>
-      <x:c r="E102" s="31"/>
-      <x:c r="F102" s="31"/>
-      <x:c r="G102" s="31" t="str">
+      <x:c r="B104" s="31"/>
+      <x:c r="C104" s="31"/>
+      <x:c r="D104" s="31"/>
+      <x:c r="E104" s="31"/>
+      <x:c r="F104" s="31"/>
+      <x:c r="G104" s="31" t="str">
         <x:v>待购预算</x:v>
       </x:c>
-      <x:c r="H102" s="32" t="e">
-        <x:f>SUMIF(材料总表!$I$5:$I$101,"待购",材料总表!$H$5:$H$101)</x:f>
+      <x:c r="H104" s="32" t="e">
+        <x:f>SUMIF(材料总表!$I$5:$I$103,"待购",材料总表!$H$5:$H$103)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
-      <x:c r="I102" s="33" t="e">
-        <x:f>COUNTIF(材料总表!$I$5:$I$101,"待购")&amp;" 项待购"</x:f>
+      <x:c r="I104" s="33" t="e">
+        <x:f>COUNTIF(材料总表!$I$5:$I$103,"待购")&amp;" 项待购"</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
-      <x:c r="J102" s="33" t="e">
-        <x:f>COUNTIF(材料总表!$J$5:$J$101,"P0 立即采购")&amp;" 项立即采购"</x:f>
+      <x:c r="J104" s="33" t="e">
+        <x:f>COUNTIF(材料总表!$J$5:$J$103,"P0 立即采购")&amp;" 项立即采购"</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
-      <x:c r="K102" s="31"/>
-      <x:c r="L102" s="34"/>
+      <x:c r="K104" s="31"/>
+      <x:c r="L104" s="34"/>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="I5:I101">
+  <x:conditionalFormatting sqref="I5:I103">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="待购"/>
   </x:conditionalFormatting>
   <x:dataValidations count="2">
-    <x:dataValidation type="list" sqref="I5:I101">
+    <x:dataValidation type="list" sqref="I5:I103">
       <x:formula1>"已有,待购,废旧自制,无需采购,可选"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="J5:J101">
+    <x:dataValidation type="list" sqref="J5:J103">
       <x:formula1>"P0 立即采购,P1 确认后,P2 后期/可选,—"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -5081,15 +5220,15 @@
         <x:v>智能日历</x:v>
       </x:c>
       <x:c r="B5" s="28" t="e">
-        <x:f>COUNTIF(材料总表!$B$5:$B$101,$A5)</x:f>
+        <x:f>COUNTIF(材料总表!$B$5:$B$103,$A5)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="C5" s="28" t="e">
-        <x:f>COUNTIFS(材料总表!$B$5:$B$101,$A5,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>COUNTIFS(材料总表!$B$5:$B$103,$A5,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="D5" s="28" t="e">
-        <x:f>SUMIFS(材料总表!$H$5:$H$101,材料总表!$B$5:$B$101,$A5,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>SUMIFS(材料总表!$H$5:$H$103,材料总表!$B$5:$B$103,$A5,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="E5" s="29" t="str"/>
@@ -5099,15 +5238,15 @@
         <x:v>折叠通信器</x:v>
       </x:c>
       <x:c r="B6" s="28" t="e">
-        <x:f>COUNTIF(材料总表!$B$5:$B$101,$A6)</x:f>
+        <x:f>COUNTIF(材料总表!$B$5:$B$103,$A6)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="C6" s="28" t="e">
-        <x:f>COUNTIFS(材料总表!$B$5:$B$101,$A6,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>COUNTIFS(材料总表!$B$5:$B$103,$A6,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="D6" s="28" t="e">
-        <x:f>SUMIFS(材料总表!$H$5:$H$101,材料总表!$B$5:$B$101,$A6,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>SUMIFS(材料总表!$H$5:$H$103,材料总表!$B$5:$B$103,$A6,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="E6" s="29" t="str"/>
@@ -5117,15 +5256,15 @@
         <x:v>齐柏林飞艇</x:v>
       </x:c>
       <x:c r="B7" s="28" t="e">
-        <x:f>COUNTIF(材料总表!$B$5:$B$101,$A7)</x:f>
+        <x:f>COUNTIF(材料总表!$B$5:$B$103,$A7)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="C7" s="28" t="e">
-        <x:f>COUNTIFS(材料总表!$B$5:$B$101,$A7,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>COUNTIFS(材料总表!$B$5:$B$103,$A7,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="D7" s="28" t="e">
-        <x:f>SUMIFS(材料总表!$H$5:$H$101,材料总表!$B$5:$B$101,$A7,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>SUMIFS(材料总表!$H$5:$H$103,材料总表!$B$5:$B$103,$A7,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="E7" s="29" t="str"/>
@@ -5135,15 +5274,15 @@
         <x:v>CL-1201</x:v>
       </x:c>
       <x:c r="B8" s="28" t="e">
-        <x:f>COUNTIF(材料总表!$B$5:$B$101,$A8)</x:f>
+        <x:f>COUNTIF(材料总表!$B$5:$B$103,$A8)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="C8" s="28" t="e">
-        <x:f>COUNTIFS(材料总表!$B$5:$B$101,$A8,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>COUNTIFS(材料总表!$B$5:$B$103,$A8,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="D8" s="28" t="e">
-        <x:f>SUMIFS(材料总表!$H$5:$H$101,材料总表!$B$5:$B$101,$A8,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>SUMIFS(材料总表!$H$5:$H$103,材料总表!$B$5:$B$103,$A8,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="E8" s="29" t="str">
@@ -5155,15 +5294,15 @@
         <x:v>自动钢琴</x:v>
       </x:c>
       <x:c r="B9" s="28" t="e">
-        <x:f>COUNTIF(材料总表!$B$5:$B$101,$A9)</x:f>
+        <x:f>COUNTIF(材料总表!$B$5:$B$103,$A9)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="C9" s="28" t="e">
-        <x:f>COUNTIFS(材料总表!$B$5:$B$101,$A9,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>COUNTIFS(材料总表!$B$5:$B$103,$A9,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="D9" s="28" t="e">
-        <x:f>SUMIFS(材料总表!$H$5:$H$101,材料总表!$B$5:$B$101,$A9,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>SUMIFS(材料总表!$H$5:$H$103,材料总表!$B$5:$B$103,$A9,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="E9" s="29" t="str"/>
@@ -5173,15 +5312,15 @@
         <x:v>助力外骨骼</x:v>
       </x:c>
       <x:c r="B10" s="28" t="e">
-        <x:f>COUNTIF(材料总表!$B$5:$B$101,$A10)</x:f>
+        <x:f>COUNTIF(材料总表!$B$5:$B$103,$A10)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="C10" s="28" t="e">
-        <x:f>COUNTIFS(材料总表!$B$5:$B$101,$A10,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>COUNTIFS(材料总表!$B$5:$B$103,$A10,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="D10" s="28" t="e">
-        <x:f>SUMIFS(材料总表!$H$5:$H$101,材料总表!$B$5:$B$101,$A10,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>SUMIFS(材料总表!$H$5:$H$103,材料总表!$B$5:$B$103,$A10,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="E10" s="29" t="str">
@@ -5193,15 +5332,15 @@
         <x:v>模型涂装</x:v>
       </x:c>
       <x:c r="B11" s="28" t="e">
-        <x:f>COUNTIF(材料总表!$B$5:$B$101,$A11)</x:f>
+        <x:f>COUNTIF(材料总表!$B$5:$B$103,$A11)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="C11" s="28" t="e">
-        <x:f>COUNTIFS(材料总表!$B$5:$B$101,$A11,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>COUNTIFS(材料总表!$B$5:$B$103,$A11,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="D11" s="28" t="e">
-        <x:f>SUMIFS(材料总表!$H$5:$H$101,材料总表!$B$5:$B$101,$A11,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>SUMIFS(材料总表!$H$5:$H$103,材料总表!$B$5:$B$103,$A11,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="E11" s="29" t="str"/>
@@ -5211,15 +5350,15 @@
         <x:v>自我介绍视频</x:v>
       </x:c>
       <x:c r="B12" s="28" t="e">
-        <x:f>COUNTIF(材料总表!$B$5:$B$101,$A12)</x:f>
+        <x:f>COUNTIF(材料总表!$B$5:$B$103,$A12)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="C12" s="28" t="e">
-        <x:f>COUNTIFS(材料总表!$B$5:$B$101,$A12,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>COUNTIFS(材料总表!$B$5:$B$103,$A12,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="D12" s="28" t="e">
-        <x:f>SUMIFS(材料总表!$H$5:$H$101,材料总表!$B$5:$B$101,$A12,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>SUMIFS(材料总表!$H$5:$H$103,材料总表!$B$5:$B$103,$A12,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="E12" s="29" t="str"/>
@@ -5229,15 +5368,15 @@
         <x:v>Minecraft模组</x:v>
       </x:c>
       <x:c r="B13" s="28" t="e">
-        <x:f>COUNTIF(材料总表!$B$5:$B$101,$A13)</x:f>
+        <x:f>COUNTIF(材料总表!$B$5:$B$103,$A13)</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="C13" s="28" t="e">
-        <x:f>COUNTIFS(材料总表!$B$5:$B$101,$A13,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>COUNTIFS(材料总表!$B$5:$B$103,$A13,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="D13" s="28" t="e">
-        <x:f>SUMIFS(材料总表!$H$5:$H$101,材料总表!$B$5:$B$101,$A13,材料总表!$I$5:$I$101,"待购")</x:f>
+        <x:f>SUMIFS(材料总表!$H$5:$H$103,材料总表!$B$5:$B$103,$A13,材料总表!$I$5:$I$103,"待购")</x:f>
         <x:v>#NAME?</x:v>
       </x:c>
       <x:c r="E13" s="29" t="str"/>
@@ -5266,6 +5405,446 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF2E5C8A"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="44" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="56" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="2">
+      <x:c r="A2" s="1" t="str">
+        <x:v>选型评审：哪些零件换过、为什么</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="2" t="str">
+        <x:v>标「已改」的已经落到材料总表；标「未改」的需要你拍板。单价仍是参考价，下单前按到手价核对。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="2" t="str">
+        <x:v>已改条目共 10 条，涉及金额变化 −1,104 元（外骨骼 −850，涂装 −254）。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="22" customHeight="1">
+      <x:c r="A5" s="21" t="str">
+        <x:v>项目</x:v>
+      </x:c>
+      <x:c r="B5" s="22" t="str">
+        <x:v>现选型</x:v>
+      </x:c>
+      <x:c r="C5" s="22" t="str">
+        <x:v>建议选型</x:v>
+      </x:c>
+      <x:c r="D5" s="22" t="str">
+        <x:v>类型</x:v>
+      </x:c>
+      <x:c r="E5" s="22" t="str">
+        <x:v>价格变化</x:v>
+      </x:c>
+      <x:c r="F5" s="22" t="str">
+        <x:v>状态</x:v>
+      </x:c>
+      <x:c r="G5" s="23" t="str">
+        <x:v>理由</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="24" t="str">
+        <x:v>助力外骨骼</x:v>
+      </x:c>
+      <x:c r="B6" s="25" t="str">
+        <x:v>大扭矩串行舵机 650 元/个 × 2</x:v>
+      </x:c>
+      <x:c r="C6" s="25" t="str">
+        <x:v>国产 70kg·cm 级串行舵机 250 元/个 × 2</x:v>
+      </x:c>
+      <x:c r="D6" s="25" t="str">
+        <x:v>降本</x:v>
+      </x:c>
+      <x:c r="E6" s="25" t="str">
+        <x:v>1,300 → 500 元</x:v>
+      </x:c>
+      <x:c r="F6" s="25" t="str">
+        <x:v>已改</x:v>
+      </x:c>
+      <x:c r="G6" s="29" t="str">
+        <x:v>讨论原文给的价位就是「单个 200~400 元」，650 元是当时随手写的估值</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="24" t="str">
+        <x:v>助力外骨骼</x:v>
+      </x:c>
+      <x:c r="B7" s="25" t="str">
+        <x:v>Arduino Mega 2560 120 元</x:v>
+      </x:c>
+      <x:c r="C7" s="25" t="str">
+        <x:v>国产兼容板 50 元</x:v>
+      </x:c>
+      <x:c r="D7" s="25" t="str">
+        <x:v>降本</x:v>
+      </x:c>
+      <x:c r="E7" s="25" t="str">
+        <x:v>120 → 50 元</x:v>
+      </x:c>
+      <x:c r="F7" s="25" t="str">
+        <x:v>已改</x:v>
+      </x:c>
+      <x:c r="G7" s="29" t="str">
+        <x:v>原文明确写「国产板 50 元」，引脚与接口完全一致</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="24" t="str">
+        <x:v>助力外骨骼</x:v>
+      </x:c>
+      <x:c r="B8" s="25" t="str">
+        <x:v>铝合金方管 10 元/根</x:v>
+      </x:c>
+      <x:c r="C8" s="25" t="str">
+        <x:v>5 元/根</x:v>
+      </x:c>
+      <x:c r="D8" s="25" t="str">
+        <x:v>降本</x:v>
+      </x:c>
+      <x:c r="E8" s="25" t="str">
+        <x:v>20 → 10 元</x:v>
+      </x:c>
+      <x:c r="F8" s="25" t="str">
+        <x:v>已改</x:v>
+      </x:c>
+      <x:c r="G8" s="29" t="str">
+        <x:v>原文写的是「5 元一根的铝合金方管」</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="24" t="str">
+        <x:v>助力外骨骼</x:v>
+      </x:c>
+      <x:c r="B9" s="25" t="str">
+        <x:v>法兰轴承（未标价）</x:v>
+      </x:c>
+      <x:c r="C9" s="25" t="str">
+        <x:v>5 元/个 × 4</x:v>
+      </x:c>
+      <x:c r="D9" s="25" t="str">
+        <x:v>补价</x:v>
+      </x:c>
+      <x:c r="E9" s="25" t="str">
+        <x:v>待估 → 20 元</x:v>
+      </x:c>
+      <x:c r="F9" s="25" t="str">
+        <x:v>已改</x:v>
+      </x:c>
+      <x:c r="G9" s="29" t="str">
+        <x:v>原文只说「几块钱」；它是防止 3D 打印件被压裂的关键件，不能省</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="24" t="str">
+        <x:v>助力外骨骼</x:v>
+      </x:c>
+      <x:c r="B10" s="25" t="str">
+        <x:v>（原先没有）</x:v>
+      </x:c>
+      <x:c r="C10" s="25" t="str">
+        <x:v>脚底薄膜压力开关 × 2</x:v>
+      </x:c>
+      <x:c r="D10" s="25" t="str">
+        <x:v>新增</x:v>
+      </x:c>
+      <x:c r="E10" s="25" t="str">
+        <x:v>— → 10 元</x:v>
+      </x:c>
+      <x:c r="F10" s="25" t="str">
+        <x:v>已改</x:v>
+      </x:c>
+      <x:c r="G10" s="29" t="str">
+        <x:v>原文的「姿态跟随」触发逻辑要用它，比力传感器便宜两个数量级</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="24" t="str">
+        <x:v>模型涂装</x:v>
+      </x:c>
+      <x:c r="B11" s="25" t="str">
+        <x:v>喷笔 0.3mm 双动 200 元</x:v>
+      </x:c>
+      <x:c r="C11" s="25" t="str">
+        <x:v>优速达 S-130（0.3mm）100 元；需要喷大面积再加 HD-130（0.5mm）80 元</x:v>
+      </x:c>
+      <x:c r="D11" s="25" t="str">
+        <x:v>降本</x:v>
+      </x:c>
+      <x:c r="E11" s="25" t="str">
+        <x:v>200 → 100 元</x:v>
+      </x:c>
+      <x:c r="F11" s="25" t="str">
+        <x:v>已改</x:v>
+      </x:c>
+      <x:c r="G11" s="29" t="str">
+        <x:v>原文点名的国产高性价比品牌就是优速达；600 元和 60 元的喷笔差距主要在雾化和手感</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="24" t="str">
+        <x:v>模型涂装</x:v>
+      </x:c>
+      <x:c r="B12" s="25" t="str">
+        <x:v>气泵 带储气罐 400 元</x:v>
+      </x:c>
+      <x:c r="C12" s="25" t="str">
+        <x:v>浩盛 AF186 mini 约 250 元</x:v>
+      </x:c>
+      <x:c r="D12" s="25" t="str">
+        <x:v>降本</x:v>
+      </x:c>
+      <x:c r="E12" s="25" t="str">
+        <x:v>400 → 250 元</x:v>
+      </x:c>
+      <x:c r="F12" s="25" t="str">
+        <x:v>已改</x:v>
+      </x:c>
+      <x:c r="G12" s="29" t="str">
+        <x:v>原文给的区间是 180-600 元，新手起步没必要顶到上限；带罐才有稳定气压</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="24" t="str">
+        <x:v>模型涂装</x:v>
+      </x:c>
+      <x:c r="B13" s="25" t="str">
+        <x:v>模型漆「一套 150 元」</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="str">
+        <x:v>郡士 H 系 / Vallejo 约 12 元/瓶 × 8 瓶</x:v>
+      </x:c>
+      <x:c r="D13" s="25" t="str">
+        <x:v>降本</x:v>
+      </x:c>
+      <x:c r="E13" s="25" t="str">
+        <x:v>150 → 96 元</x:v>
+      </x:c>
+      <x:c r="F13" s="25" t="str">
+        <x:v>已改</x:v>
+      </x:c>
+      <x:c r="G13" s="29" t="str">
+        <x:v>原文：郡士 H 系 10-15 元/瓶、Vallejo 15-20 元/瓶；按色号买比买整套省</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="24" t="str">
+        <x:v>模型涂装</x:v>
+      </x:c>
+      <x:c r="B14" s="25" t="str">
+        <x:v>排风抽风机 100 元</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="str">
+        <x:v>自制负压喷漆箱约 150 元（含风机、灯条、过滤棉）</x:v>
+      </x:c>
+      <x:c r="D14" s="25" t="str">
+        <x:v>升级</x:v>
+      </x:c>
+      <x:c r="E14" s="25" t="str">
+        <x:v>100 → 150 元</x:v>
+      </x:c>
+      <x:c r="F14" s="25" t="str">
+        <x:v>已改</x:v>
+      </x:c>
+      <x:c r="G14" s="29" t="str">
+        <x:v>原文有「100 元自制负压箱（不含风机）」的方案；负压箱挡漆雾比单台排气扇有效得多</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="24" t="str">
+        <x:v>模型涂装</x:v>
+      </x:c>
+      <x:c r="B15" s="25" t="str">
+        <x:v>（原先没有）</x:v>
+      </x:c>
+      <x:c r="C15" s="25" t="str">
+        <x:v>手持充电喷笔套装 约 150 元</x:v>
+      </x:c>
+      <x:c r="D15" s="25" t="str">
+        <x:v>新增·可选</x:v>
+      </x:c>
+      <x:c r="E15" s="25" t="str">
+        <x:v>— → 150 元</x:v>
+      </x:c>
+      <x:c r="F15" s="25" t="str">
+        <x:v>已加为可选</x:v>
+      </x:c>
+      <x:c r="G15" s="29" t="str">
+        <x:v>原文：无需气泵、约 74-200 元；适合先试试有没有兴趣，与喷笔+气泵二选一</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="24" t="str">
+        <x:v>智能日历</x:v>
+      </x:c>
+      <x:c r="B16" s="25" t="str">
+        <x:v>步进电机 + ULN2003 共 9 元</x:v>
+      </x:c>
+      <x:c r="C16" s="25" t="str">
+        <x:v>旧光驱拆解（0 元）</x:v>
+      </x:c>
+      <x:c r="D16" s="25" t="str">
+        <x:v>降本</x:v>
+      </x:c>
+      <x:c r="E16" s="25" t="str">
+        <x:v>9 → 0 元</x:v>
+      </x:c>
+      <x:c r="F16" s="25" t="str">
+        <x:v>未改，看家里备料</x:v>
+      </x:c>
+      <x:c r="G16" s="29" t="str">
+        <x:v>原文清单写的就是「采购或旧光驱拆解」，家里有废弃光驱就白拿</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="24" t="str">
+        <x:v>折叠通信器</x:v>
+      </x:c>
+      <x:c r="B17" s="25" t="str">
+        <x:v>LoRa SX1278（Ra-02）25 元</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="str">
+        <x:v>SX1262（如 E22 系列）约 35 元</x:v>
+      </x:c>
+      <x:c r="D17" s="25" t="str">
+        <x:v>升级</x:v>
+      </x:c>
+      <x:c r="E17" s="25" t="str">
+        <x:v>25 → 35 元</x:v>
+      </x:c>
+      <x:c r="F17" s="25" t="str">
+        <x:v>未改，待你定</x:v>
+      </x:c>
+      <x:c r="G17" s="29" t="str">
+        <x:v>灵敏度与功耗都更好，T-Deck 旗舰版用的就是 SX1262；但接线和代码要跟着改，经济版先跑通的话不必换</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="24" t="str">
+        <x:v>折叠通信器</x:v>
+      </x:c>
+      <x:c r="B18" s="25" t="str">
+        <x:v>2.42 寸 OLED SSD1309 50 元</x:v>
+      </x:c>
+      <x:c r="C18" s="25" t="str">
+        <x:v>2.4 寸 ST7789 SPI 彩屏 约 30 元</x:v>
+      </x:c>
+      <x:c r="D18" s="25" t="str">
+        <x:v>替代</x:v>
+      </x:c>
+      <x:c r="E18" s="25" t="str">
+        <x:v>50 → 30 元</x:v>
+      </x:c>
+      <x:c r="F18" s="25" t="str">
+        <x:v>未改，待你定</x:v>
+      </x:c>
+      <x:c r="G18" s="29" t="str">
+        <x:v>彩屏更便宜也更大，但 OLED 免背光、暗处更干净，且现有代码是 U8g2 SSD1309；换屏要改代码和遮光窗</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="24" t="str">
+        <x:v>ESP32 自动钢琴</x:v>
+      </x:c>
+      <x:c r="B19" s="25" t="str">
+        <x:v>24 个 JF-0530B 8 元/个</x:v>
+      </x:c>
+      <x:c r="C19" s="25" t="str">
+        <x:v>先买 2 个验证，再对比批量价与拆机件</x:v>
+      </x:c>
+      <x:c r="D19" s="25" t="str">
+        <x:v>比价</x:v>
+      </x:c>
+      <x:c r="E19" s="25" t="str">
+        <x:v>192 元（单项最大）</x:v>
+      </x:c>
+      <x:c r="F19" s="25" t="str">
+        <x:v>未改</x:v>
+      </x:c>
+      <x:c r="G19" s="29" t="str">
+        <x:v>这是全表最大的一笔单项支出；敲击力度和声音不达标的话，方案要改，先别囤 24 个</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="24" t="str">
+        <x:v>齐柏林飞艇</x:v>
+      </x:c>
+      <x:c r="B20" s="25" t="str">
+        <x:v>细碳纤维棒 1m 装 25 元</x:v>
+      </x:c>
+      <x:c r="C20" s="25" t="str">
+        <x:v>翻了家里的风筝骨架 / 旧鱼竿 / 旧伞骨再说</x:v>
+      </x:c>
+      <x:c r="D20" s="25" t="str">
+        <x:v>降本</x:v>
+      </x:c>
+      <x:c r="E20" s="25" t="str">
+        <x:v>25 → 可能 0 元</x:v>
+      </x:c>
+      <x:c r="F20" s="25" t="str">
+        <x:v>未改，可选</x:v>
+      </x:c>
+      <x:c r="G20" s="29" t="str">
+        <x:v>0.5-1.0mm 细碳棒在这类物品里很常见，先找后买</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="35" t="str">
+        <x:v>共用工具</x:v>
+      </x:c>
+      <x:c r="B21" s="36" t="str">
+        <x:v>万用表（已有，曾受腐蚀）</x:v>
+      </x:c>
+      <x:c r="C21" s="36" t="str">
+        <x:v>先校对；不准则换优利德 UT33+ 约 50 元</x:v>
+      </x:c>
+      <x:c r="D21" s="36" t="str">
+        <x:v>替换</x:v>
+      </x:c>
+      <x:c r="E21" s="36" t="str">
+        <x:v>0 → 50 元</x:v>
+      </x:c>
+      <x:c r="F21" s="36" t="str">
+        <x:v>未改</x:v>
+      </x:c>
+      <x:c r="G21" s="37" t="str">
+        <x:v>全部电子项目都靠它量电压，读数不准会把 7.5V 调错、烧模块（台历的 SX1308 调压尤其依赖它）</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:conditionalFormatting sqref="D6:D21">
+    <x:cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="降本"/>
+    <x:cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="升级"/>
+    <x:cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="新增"/>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="F6:F21">
+    <x:cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="已"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="F6:F21">
+      <x:formula1>"已改,未改,未改，待你定,未改，可选,未改，看家里备料,已加为可选"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:tabColor rgb="FF2E5C8A"/>
@@ -5324,7 +5903,7 @@
       <x:c r="C5" s="27" t="str">
         <x:v>已有</x:v>
       </x:c>
-      <x:c r="D5" s="36" t="n">
+      <x:c r="D5" s="39" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E5" s="25" t="str">
@@ -5345,7 +5924,7 @@
       <x:c r="C6" s="27" t="str">
         <x:v>已有</x:v>
       </x:c>
-      <x:c r="D6" s="36" t="n">
+      <x:c r="D6" s="39" t="n">
         <x:v>80</x:v>
       </x:c>
       <x:c r="E6" s="25" t="str">
@@ -5368,7 +5947,7 @@
       <x:c r="C7" s="27" t="str">
         <x:v>已有</x:v>
       </x:c>
-      <x:c r="D7" s="36" t="n">
+      <x:c r="D7" s="39" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E7" s="25" t="str">
@@ -5389,7 +5968,7 @@
       <x:c r="C8" s="27" t="str">
         <x:v>已有</x:v>
       </x:c>
-      <x:c r="D8" s="36" t="n">
+      <x:c r="D8" s="39" t="n">
         <x:v>1200</x:v>
       </x:c>
       <x:c r="E8" s="25" t="str">
@@ -5412,7 +5991,7 @@
       <x:c r="C9" s="27" t="str">
         <x:v>已有</x:v>
       </x:c>
-      <x:c r="D9" s="36" t="n">
+      <x:c r="D9" s="39" t="n">
         <x:v>200</x:v>
       </x:c>
       <x:c r="E9" s="25" t="str">
@@ -5435,7 +6014,7 @@
       <x:c r="C10" s="27" t="str">
         <x:v>已有</x:v>
       </x:c>
-      <x:c r="D10" s="36" t="n">
+      <x:c r="D10" s="39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="E10" s="25" t="str">
@@ -5458,7 +6037,7 @@
       <x:c r="C11" s="27" t="str">
         <x:v>已有</x:v>
       </x:c>
-      <x:c r="D11" s="36" t="n">
+      <x:c r="D11" s="39" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E11" s="25" t="str">
@@ -5479,7 +6058,7 @@
       <x:c r="C12" s="27" t="str">
         <x:v>待购</x:v>
       </x:c>
-      <x:c r="D12" s="36" t="n">
+      <x:c r="D12" s="39" t="n">
         <x:v>25</x:v>
       </x:c>
       <x:c r="E12" s="25" t="str">
@@ -5502,7 +6081,7 @@
       <x:c r="C13" s="27" t="str">
         <x:v>待购</x:v>
       </x:c>
-      <x:c r="D13" s="36" t="n">
+      <x:c r="D13" s="39" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="E13" s="25" t="str">
@@ -5523,7 +6102,7 @@
       <x:c r="C14" s="27" t="str">
         <x:v>待购</x:v>
       </x:c>
-      <x:c r="D14" s="36" t="n">
+      <x:c r="D14" s="39" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="E14" s="25" t="str">
@@ -5544,7 +6123,7 @@
       <x:c r="C15" s="27" t="str">
         <x:v>已有</x:v>
       </x:c>
-      <x:c r="D15" s="36" t="n">
+      <x:c r="D15" s="39" t="n">
         <x:v>40</x:v>
       </x:c>
       <x:c r="E15" s="25" t="str">
@@ -5565,7 +6144,7 @@
       <x:c r="C16" s="27" t="str">
         <x:v>已有</x:v>
       </x:c>
-      <x:c r="D16" s="36" t="n">
+      <x:c r="D16" s="39" t="n">
         <x:v>15</x:v>
       </x:c>
       <x:c r="E16" s="25" t="str">
@@ -5586,7 +6165,7 @@
       <x:c r="C17" s="27" t="str">
         <x:v>已有</x:v>
       </x:c>
-      <x:c r="D17" s="36" t="n">
+      <x:c r="D17" s="39" t="n">
         <x:v>50</x:v>
       </x:c>
       <x:c r="E17" s="25" t="str">
@@ -5598,31 +6177,31 @@
       <x:c r="G17" s="29" t="str"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="37" t="str">
+      <x:c r="A18" s="35" t="str">
         <x:v>喷笔 + 气泵</x:v>
       </x:c>
-      <x:c r="B18" s="38" t="str">
+      <x:c r="B18" s="36" t="str">
         <x:v>模型涂装</x:v>
       </x:c>
-      <x:c r="C18" s="39" t="str">
-        <x:v>待购</x:v>
-      </x:c>
-      <x:c r="D18" s="40" t="n">
+      <x:c r="C18" s="40" t="str">
+        <x:v>待购</x:v>
+      </x:c>
+      <x:c r="D18" s="41" t="n">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="E18" s="38" t="str">
+      <x:c r="E18" s="36" t="str">
         <x:v>阳台工作台</x:v>
       </x:c>
-      <x:c r="F18" s="38" t="str">
+      <x:c r="F18" s="36" t="str">
         <x:v>飞艇、涂装工位</x:v>
       </x:c>
-      <x:c r="G18" s="41" t="str">
+      <x:c r="G18" s="37" t="str">
         <x:v>见模型涂装材料行</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="C5:C18">
-    <x:cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="待购"/>
+    <x:cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="待购"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="C5:C18">
@@ -5633,7 +6212,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:tabColor rgb="FF2E5C8A"/>
@@ -5867,22 +6446,22 @@
       </x:c>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="37" t="str">
+      <x:c r="A13" s="35" t="str">
         <x:v>Minecraft模组</x:v>
       </x:c>
-      <x:c r="B13" s="38" t="str">
+      <x:c r="B13" s="36" t="str">
         <x:v>方案已定，待搭环境</x:v>
       </x:c>
-      <x:c r="C13" s="38" t="str">
+      <x:c r="C13" s="36" t="str">
         <x:v>暂无实物</x:v>
       </x:c>
-      <x:c r="D13" s="38" t="str">
+      <x:c r="D13" s="36" t="str">
         <x:v>未公开</x:v>
       </x:c>
-      <x:c r="E13" s="38" t="str">
+      <x:c r="E13" s="36" t="str">
         <x:v>—</x:v>
       </x:c>
-      <x:c r="F13" s="38" t="str">
+      <x:c r="F13" s="36" t="str">
         <x:v>定 Forge 1.20.1，先跑通一个空模组</x:v>
       </x:c>
       <x:c r="G13" s="43" t="str">
@@ -5891,8 +6470,8 @@
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="G5:G13">
-    <x:cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="待处理"/>
-    <x:cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="已完成"/>
+    <x:cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="待处理"/>
+    <x:cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="已完成"/>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="G5:G13">
@@ -5903,7 +6482,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:tabColor rgb="FF7F7F7F"/>
@@ -6100,6 +6679,36 @@
         <x:v>对账提醒：自动钢琴原讨论写的「约 1400 元」与其物料表逐项相加的 634 元对不上，本表按 634 元计。</x:v>
       </x:c>
     </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="67" t="str"/>
+      <x:c r="B28" s="71" t="str">
+        <x:v>六、选型与比价</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="67" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B29" s="70" t="str">
+        <x:v>2026-10-16 做过一轮选型评审，见「选型评审」工作表：已改 10 条，助力外骨骼 −850 元、模型涂装 −254 元，全表待购预算 −1,104 元。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="67" t="str">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B30" s="70" t="str">
+        <x:v>单价是参考价，不是实时报价。同一型号在不同店铺差几十元很正常，下单前请按到手价核对，有差价回填「单价」列。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="67" t="str">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B31" s="70" t="str">
+        <x:v>外骨骼的舵机、钢琴的电磁铁是两笔最大的支出，都建议先买最小数量验证（舵机 1 个、电磁铁 2 个）再批量下单。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/projects/材料与采购规划.xlsx
+++ b/projects/材料与采购规划.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Ra99ac5711fad499e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材料总表" sheetId="2" r:id="Re207bb8313bc4d60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分项预算" sheetId="3" r:id="R6f259d3706ae40c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="选型评审" sheetId="4" r:id="R47b46b8b289e4134"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工具与设备" sheetId="5" r:id="Rb0feb17813d64bef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="线上线下同步" sheetId="6" r:id="R60dde0911d474ef7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="7" r:id="Rfcd5ae423b45414d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R0b2b42bb4edf43a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="材料总表" sheetId="2" r:id="R9a9af4b684dc4290"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分项预算" sheetId="3" r:id="Rb2f85f786c704c18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="选型评审" sheetId="4" r:id="R838b2a3cf1604d3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工具与设备" sheetId="5" r:id="Ref307d54b0de4007"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="线上线下同步" sheetId="6" r:id="Rdbd4a1a2b0374f8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="7" r:id="R300e2d2fa4c546eb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1098,13 +1098,13 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="24" t="str">
-        <x:v>先出图纸再做实物</x:v>
+        <x:v>图纸已出，照着备料</x:v>
       </x:c>
       <x:c r="B34" s="25" t="str">
         <x:v>齐柏林飞艇</x:v>
       </x:c>
       <x:c r="C34" s="29" t="str">
-        <x:v>图纸 PDF 与 STL 先完成，才能按图纸裁碳棒，避免材料切错</x:v>
+        <x:v>1:1 图纸 PDF 与 STL 已入库（v1），按 F01-F16 弯隔框、裁蒙皮；还缺尾翼尺寸</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -6318,13 +6318,13 @@
         <x:v>1:1000 图纸、碳棒、PP 蒙皮</x:v>
       </x:c>
       <x:c r="D7" s="25" t="str">
-        <x:v>计划开源图纸与 STL</x:v>
+        <x:v>图纸与 STL 已出 v1（待补尾翼）</x:v>
       </x:c>
       <x:c r="E7" s="25" t="str">
-        <x:v>B 站视频说明区 + 网盘链接</x:v>
+        <x:v>已入库 projects/模型/图纸与模型</x:v>
       </x:c>
       <x:c r="F7" s="25" t="str">
-        <x:v>先出图纸 PDF 与 STL 再按表备料；开源文件写清版本号</x:v>
+        <x:v>按 F01-F16 备料；定下尾翼展长/弦长/根部站位后补尾翼模型</x:v>
       </x:c>
       <x:c r="G7" s="42" t="str">
         <x:v>待处理</x:v>
